--- a/artfynd/A 4555-2021 artfynd.xlsx
+++ b/artfynd/A 4555-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4555-2021 artfynd.xlsx
+++ b/artfynd/A 4555-2021 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>120976772</v>
       </c>
       <c r="B9" t="n">
-        <v>79715</v>
+        <v>79718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120976771</v>
+        <v>120976770</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>367600</v>
+        <v>367609</v>
       </c>
       <c r="R10" t="n">
-        <v>6746166</v>
+        <v>6746156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120976770</v>
+        <v>120976771</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>367609</v>
+        <v>367600</v>
       </c>
       <c r="R11" t="n">
-        <v>6746156</v>
+        <v>6746166</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>120976768</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 4555-2021 artfynd.xlsx
+++ b/artfynd/A 4555-2021 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120976772</v>
+        <v>120976771</v>
       </c>
       <c r="B9" t="n">
-        <v>79718</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120976771</v>
+        <v>120976772</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 4555-2021 artfynd.xlsx
+++ b/artfynd/A 4555-2021 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120976771</v>
+        <v>120976768</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>79714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>367600</v>
+        <v>367609</v>
       </c>
       <c r="R9" t="n">
-        <v>6746166</v>
+        <v>6746156</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
         <v>120976770</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120976772</v>
+        <v>120976771</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120976768</v>
+        <v>120976772</v>
       </c>
       <c r="B12" t="n">
-        <v>79711</v>
+        <v>79721</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>367609</v>
+        <v>367600</v>
       </c>
       <c r="R12" t="n">
-        <v>6746156</v>
+        <v>6746166</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
